--- a/results/Int All Data -0.8/Rando_1_permute.xlsx
+++ b/results/Int All Data -0.8/Rando_1_permute.xlsx
@@ -440,57 +440,57 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8127027154485348</v>
+        <v>0.816658838176622</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8127027154485348</v>
+        <v>0.8163198551257747</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8105473340690228</v>
+        <v>0.8129300246173</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.808027503466229</v>
+        <v>0.8136079907189949</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8056448129179518</v>
+        <v>0.8193707025834017</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8047238806674024</v>
+        <v>0.8237774822444186</v>
       </c>
     </row>
     <row r="8">
@@ -500,557 +500,557 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8045671222281958</v>
+        <v>0.8282450034426492</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8096067834337832</v>
+        <v>0.8289837110815578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8042594531375268</v>
+        <v>0.8242986899069069</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8042594531375268</v>
+        <v>0.8213085839864935</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8040419531611065</v>
+        <v>0.8084370372466352</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.808397800477255</v>
+        <v>0.8115231600690416</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.819666487460268</v>
+        <v>0.8068381388943908</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.819666487460268</v>
+        <v>0.8046474821500995</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8195450043858408</v>
+        <v>0.8076023127057337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8179010214764721</v>
+        <v>0.8081587957330013</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8172230553747771</v>
+        <v>0.8068028635296115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8155888816577535</v>
+        <v>0.8080020372937947</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8157103647321807</v>
+        <v>0.8069243466040388</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8137979495015233</v>
+        <v>0.8040557237580526</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8083742206879639</v>
+        <v>0.8052294313498014</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8046806824934212</v>
+        <v>0.80596813898871</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8046101317638625</v>
+        <v>0.8051079482753742</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8040281825641606</v>
+        <v>0.8028565499938694</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8040281825641606</v>
+        <v>0.8025175669430218</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8049491148147101</v>
+        <v>0.802735066919442</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8088601529856729</v>
+        <v>0.8023960838685945</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8116582251021005</v>
+        <v>0.8022138592569537</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8130494326702696</v>
+        <v>0.8022138592569537</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8123714665685747</v>
+        <v>0.8017533931316789</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8102062759967177</v>
+        <v>0.8042477575620384</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8211497505258293</v>
+        <v>0.8042477575620384</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8209577167218434</v>
+        <v>0.8006757024419229</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8199760429340803</v>
+        <v>0.7993805117757468</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8127711911566358</v>
+        <v>0.7987632872112655</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8161002801278967</v>
+        <v>0.7984850456976316</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8204619752317893</v>
+        <v>0.799405977948181</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8199662337417353</v>
+        <v>0.7996842194618149</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7788415721117117</v>
+        <v>0.8009186685907774</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7833090933099421</v>
+        <v>0.8015966346924723</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7813614027145053</v>
+        <v>0.8015966346924723</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7830563179687426</v>
+        <v>0.797928562670364</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7979715722060308</v>
+        <v>0.797928562670364</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7991452797977797</v>
+        <v>0.7985457872348453</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7984673136960848</v>
+        <v>0.8061856389651303</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8174209369665073</v>
+        <v>0.8085585203210623</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8172954924874791</v>
+        <v>0.8085585203210623</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8171642002207069</v>
+        <v>0.808219537270215</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8227446874734727</v>
+        <v>0.8139469737698424</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8078941361779991</v>
+        <v>0.821551550135348</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8066244116842571</v>
+        <v>0.8252803636946699</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8130396234779246</v>
+        <v>0.8234639653660054</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8102062759967177</v>
+        <v>0.8296264018184734</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7978108523622233</v>
+        <v>0.8246984144949681</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8121481188044104</v>
+        <v>0.8362962753364835</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8121481188044104</v>
+        <v>0.8362962753364835</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7975561906378805</v>
+        <v>0.8364784999481245</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7962002584344906</v>
+        <v>0.8341918263018402</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7822764871773106</v>
+        <v>0.8319404280203352</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.781816021052036</v>
+        <v>0.8312624619186403</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7727693047734925</v>
+        <v>0.8472201314809051</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7807070164021014</v>
+        <v>0.8453077162502476</v>
       </c>
     </row>
     <row r="64">
@@ -1060,657 +1060,657 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7892168680380671</v>
+        <v>0.8374875262914651</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7120032445790064</v>
+        <v>0.8374875262914651</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7129594521943352</v>
+        <v>0.8478137762560953</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7129594521943352</v>
+        <v>0.829530196278166</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7106473123756165</v>
+        <v>0.8271729719023231</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7110470369636777</v>
+        <v>0.8271729719023231</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.701869028418362</v>
+        <v>0.8253467643813135</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6985242824670119</v>
+        <v>0.822462484555238</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7039480112805712</v>
+        <v>0.8159454080718335</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6971683502636221</v>
+        <v>0.8189805985493713</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6722501721324619</v>
+        <v>0.8182320817181178</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6871301510049705</v>
+        <v>0.8132688190298332</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6921541552304689</v>
+        <v>0.8090442639804571</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7153264857625232</v>
+        <v>0.8066164888750553</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6786555747337841</v>
+        <v>0.7921969761278214</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6768391764051196</v>
+        <v>0.7992803448308385</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6714252567839054</v>
+        <v>0.8101983531875159</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6687741339143394</v>
+        <v>0.8118932684417532</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6687741339143394</v>
+        <v>0.8129905775161994</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6566922271582581</v>
+        <v>0.8105471454307085</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6590651085141903</v>
+        <v>0.8102689039170746</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6567627778878168</v>
+        <v>0.8162178017977232</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6564237948369693</v>
+        <v>0.8265440517623535</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6535297058185487</v>
+        <v>0.8333589881440819</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6434816973675523</v>
+        <v>0.8223645812701017</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6548758288295935</v>
+        <v>0.8133942635088613</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6252373541590033</v>
+        <v>0.8135764881205021</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6299733076785226</v>
+        <v>0.8099789668279525</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6305297907057903</v>
+        <v>0.8099789668279525</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6292953415768276</v>
+        <v>0.8104394329532272</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6292953415768276</v>
+        <v>0.8046218273393508</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6260622695075597</v>
+        <v>0.8046218273393508</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5949209133867179</v>
+        <v>0.7925086066230912</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5668794506852287</v>
+        <v>0.7909449836356262</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5814713788517586</v>
+        <v>0.7462580760778321</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5616986880205239</v>
+        <v>0.6370508285937957</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5638540694000358</v>
+        <v>0.6360593456136876</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5635150863491883</v>
+        <v>0.6050081586070947</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5693385397508088</v>
+        <v>0.5805798741782443</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.564263603180442</v>
+        <v>0.5948779038510512</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5706690057817644</v>
+        <v>0.5841872046631391</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5607777557699745</v>
+        <v>0.5845261877139866</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5474104675400621</v>
+        <v>0.5765218867604199</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5423453401620404</v>
+        <v>0.5761829037095725</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5416066325231318</v>
+        <v>0.5760418022504551</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5297618441281609</v>
+        <v>0.5730105731775181</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5297618441281609</v>
+        <v>0.5730105731775181</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5285724795563227</v>
+        <v>0.5727323316638843</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5297716533205059</v>
+        <v>0.5456372673853787</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5332575007309734</v>
+        <v>0.5456372673853787</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5326598945511823</v>
+        <v>0.5369255727530818</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5317997038378466</v>
+        <v>0.529887288607189</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5292093225054941</v>
+        <v>0.5292544070626185</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.534981843562246</v>
+        <v>0.5289154240117711</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.534981843562246</v>
+        <v>0.5289154240117711</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.534981843562246</v>
+        <v>0.5328362713750789</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5403506786263358</v>
+        <v>0.5471597672203201</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5485724795563227</v>
+        <v>0.5523659960574592</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5821885817228337</v>
+        <v>0.5547388774133915</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5828410816520944</v>
+        <v>0.5187910170434717</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5828410816520944</v>
+        <v>0.5232585382417023</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5883255520028673</v>
+        <v>0.5232585382417023</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.582025975495883</v>
+        <v>0.5280043009535667</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5815302340058289</v>
+        <v>0.5286822670552616</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5815302340058289</v>
+        <v>0.5270226271658036</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5787751714250682</v>
+        <v>0.5310296822387595</v>
       </c>
     </row>
     <row r="130">
@@ -1720,267 +1720,267 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5590141761693217</v>
+        <v>0.5104379238467125</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5593531592201693</v>
+        <v>0.5104379238467125</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5608403836903313</v>
+        <v>0.5104379238467125</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5167373117153825</v>
+        <v>0.510098940795865</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5141920149401544</v>
+        <v>0.5141667374060345</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5169646208841477</v>
+        <v>0.5151836865585769</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5087369721664167</v>
+        <v>0.5151836865585769</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5078669722607358</v>
+        <v>0.5226060383124417</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5078669722607358</v>
+        <v>0.5298814408194449</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5082568876564519</v>
+        <v>0.5003997245880611</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5138020995444385</v>
+        <v>0.5010776906897561</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5138020995444385</v>
+        <v>0.5000607415372137</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5133063580543844</v>
+        <v>0.5003997245880611</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5184048744140423</v>
+        <v>0.5003997245880611</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5188398743668826</v>
+        <v>0.5007387076389086</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5188398743668826</v>
+        <v>0.5007387076389086</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5174133914339342</v>
+        <v>0.5007387076389086</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5102125010610905</v>
+        <v>0.5007387076389086</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5102125010610905</v>
+        <v>0.5000254661724343</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5085077766145082</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5091093441989003</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5111177763315508</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5111177763315508</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5078279241296699</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5041441951274723</v>
+        <v>0.5003997245880611</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5040834535902587</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.498022881827528</v>
+        <v>0.5003389830508475</v>
       </c>
     </row>
   </sheetData>
